--- a/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_mlp_nn_vs_sc/mlp_nn_vs_sc_classB_Ru48_Rv48_snr6dB.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_mlp_nn_vs_sc/mlp_nn_vs_sc_classB_Ru48_Rv48_snr6dB.xlsx
@@ -61,9 +61,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,19 +427,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -550,7 +537,7 @@
         <v>0.4844</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0313</v>
+        <v>0.031</v>
       </c>
       <c r="G6" t="n">
         <v>0.025</v>
@@ -579,7 +566,7 @@
         <v>0.4844</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0317</v>
+        <v>0.032</v>
       </c>
       <c r="G7" t="n">
         <v>0.015</v>
@@ -608,13 +595,13 @@
         <v>0.4805</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0265</v>
+        <v>0.025</v>
       </c>
       <c r="G8" t="n">
         <v>0.005</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
         <v>5000</v>
@@ -666,29 +653,16 @@
         <v>0.4814</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>0.0003</v>
       </c>
       <c r="H10" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="I10" t="n">
         <v>500</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Capacity</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.688195269487774</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.688195269487774</v>
       </c>
     </row>
   </sheetData>

--- a/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_mlp_nn_vs_sc/mlp_nn_vs_sc_classB_Ru48_Rv48_snr6dB.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_mlp_nn_vs_sc/mlp_nn_vs_sc_classB_Ru48_Rv48_snr6dB.xlsx
@@ -598,13 +598,13 @@
         <v>0.025</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005</v>
+        <v>0.0046</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>5.43</v>
       </c>
       <c r="I8" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="9">
@@ -627,13 +627,13 @@
         <v>0.045</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="H9" t="n">
-        <v>45</v>
+        <v>37.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="10">
@@ -656,13 +656,13 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003</v>
+        <v>0.0009</v>
       </c>
       <c r="H10" t="n">
-        <v>230</v>
+        <v>76.67</v>
       </c>
       <c r="I10" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_mlp_nn_vs_sc/mlp_nn_vs_sc_classB_Ru48_Rv48_snr6dB.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_mlp_nn_vs_sc/mlp_nn_vs_sc_classB_Ru48_Rv48_snr6dB.xlsx
@@ -444,6 +444,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -627,10 +628,10 @@
         <v>0.045</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="H9" t="n">
-        <v>37.5</v>
+        <v>40.91</v>
       </c>
       <c r="I9" t="n">
         <v>10000</v>
@@ -656,10 +657,10 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>76.67</v>
+        <v>69</v>
       </c>
       <c r="I10" t="n">
         <v>10000</v>

--- a/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_mlp_nn_vs_sc/mlp_nn_vs_sc_classB_Ru48_Rv48_snr6dB.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_mlp_nn_vs_sc/mlp_nn_vs_sc_classB_Ru48_Rv48_snr6dB.xlsx
@@ -444,7 +444,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -512,10 +511,10 @@
         <v>0.04</v>
       </c>
       <c r="G5" t="n">
-        <v>0.046</v>
+        <v>0.0456</v>
       </c>
       <c r="H5" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="I5" t="n">
         <v>5000</v>
@@ -541,10 +540,10 @@
         <v>0.031</v>
       </c>
       <c r="G6" t="n">
-        <v>0.025</v>
+        <v>0.0246</v>
       </c>
       <c r="H6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="I6" t="n">
         <v>5000</v>
@@ -570,10 +569,10 @@
         <v>0.032</v>
       </c>
       <c r="G7" t="n">
-        <v>0.015</v>
+        <v>0.01585</v>
       </c>
       <c r="H7" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="I7" t="n">
         <v>5000</v>
@@ -599,10 +598,10 @@
         <v>0.025</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0046</v>
+        <v>0.004567</v>
       </c>
       <c r="H8" t="n">
-        <v>5.43</v>
+        <v>5.47</v>
       </c>
       <c r="I8" t="n">
         <v>10000</v>
@@ -628,10 +627,10 @@
         <v>0.045</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0011</v>
+        <v>0.00106</v>
       </c>
       <c r="H9" t="n">
-        <v>40.91</v>
+        <v>42.45</v>
       </c>
       <c r="I9" t="n">
         <v>10000</v>
@@ -657,10 +656,10 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001</v>
+        <v>0.00102</v>
       </c>
       <c r="H10" t="n">
-        <v>69</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>10000</v>

--- a/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_mlp_nn_vs_sc/mlp_nn_vs_sc_classB_Ru48_Rv48_snr6dB.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classB_Ru48_Rv48_mlp_nn_vs_sc/mlp_nn_vs_sc_classB_Ru48_Rv48_snr6dB.xlsx
@@ -537,16 +537,16 @@
         <v>0.4844</v>
       </c>
       <c r="F6" t="n">
-        <v>0.031</v>
+        <v>0.0258</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0246</v>
+        <v>0.025</v>
       </c>
       <c r="H6" t="n">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="I6" t="n">
-        <v>5000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         <v>0.4844</v>
       </c>
       <c r="F7" t="n">
-        <v>0.032</v>
+        <v>0.0227</v>
       </c>
       <c r="G7" t="n">
         <v>0.01585</v>
       </c>
       <c r="H7" t="n">
-        <v>2.02</v>
+        <v>1.43</v>
       </c>
       <c r="I7" t="n">
-        <v>5000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="8">
@@ -595,16 +595,16 @@
         <v>0.4805</v>
       </c>
       <c r="F8" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004567</v>
+        <v>0.0046</v>
       </c>
       <c r="H8" t="n">
-        <v>5.47</v>
+        <v>4.35</v>
       </c>
       <c r="I8" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="9">
@@ -627,13 +627,13 @@
         <v>0.045</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00106</v>
+        <v>0.0011</v>
       </c>
       <c r="H9" t="n">
-        <v>42.45</v>
+        <v>40.91</v>
       </c>
       <c r="I9" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="10">
@@ -656,13 +656,13 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00102</v>
+        <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>67.65000000000001</v>
+        <v>69</v>
       </c>
       <c r="I10" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
   </sheetData>
